--- a/Project2/sprint_backlogs/SprintBacklog042025.xlsx
+++ b/Project2/sprint_backlogs/SprintBacklog042025.xlsx
@@ -518,10 +518,9 @@
       <c r="C8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="4"/>
     </row>
     <row r="9">
       <c r="B9" s="1"/>
@@ -547,10 +546,9 @@
       <c r="C11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="4"/>
     </row>
     <row r="12">
       <c r="A12" s="1"/>
